--- a/output/tables/2025/tabla3_variables_secundarias.xlsx
+++ b/output/tables/2025/tabla3_variables_secundarias.xlsx
@@ -635,64 +635,72 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>6840298</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>51.45</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="2" t="n">
         <v>51.45</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1603714</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12.06</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>1603714</v>
+        <v>5579658</v>
       </c>
       <c r="E5" t="n">
-        <v>12.06</v>
+        <v>41.96</v>
       </c>
       <c r="F5" t="n">
-        <v>12.06</v>
+        <v>41.96</v>
       </c>
       <c r="G5" t="n">
-        <v>12.06</v>
+        <v>54.03</v>
       </c>
     </row>
     <row r="6">
@@ -700,22 +708,22 @@
         <v>14</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>5579658</v>
+        <v>6059687</v>
       </c>
       <c r="E6" t="n">
-        <v>41.96</v>
+        <v>45.58</v>
       </c>
       <c r="F6" t="n">
-        <v>41.96</v>
+        <v>45.58</v>
       </c>
       <c r="G6" t="n">
-        <v>54.03</v>
+        <v>99.6</v>
       </c>
     </row>
     <row r="7">
@@ -723,1230 +731,1012 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>6059687</v>
+        <v>32299</v>
       </c>
       <c r="E7" t="n">
-        <v>45.58</v>
+        <v>0.24</v>
       </c>
       <c r="F7" t="n">
-        <v>45.58</v>
+        <v>0.24</v>
       </c>
       <c r="G7" t="n">
-        <v>99.6</v>
+        <v>99.84</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="n">
-        <v>96</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="n">
-        <v>32299</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G8" t="n">
-        <v>99.84</v>
+      <c r="B8" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>20699</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>20699</v>
+        <v>3315823</v>
       </c>
       <c r="E9" t="n">
-        <v>0.16</v>
+        <v>24.94</v>
       </c>
       <c r="F9" t="n">
-        <v>0.16</v>
+        <v>24.94</v>
       </c>
       <c r="G9" t="n">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6892304</v>
+      </c>
+      <c r="E10" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="F10" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="G10" t="n">
+        <v>76.78</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>3087931</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>100</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3315823</v>
-      </c>
-      <c r="E11" t="n">
-        <v>24.94</v>
-      </c>
-      <c r="F11" t="n">
-        <v>24.94</v>
-      </c>
-      <c r="G11" t="n">
-        <v>24.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>6892304</v>
+        <v>5461080</v>
       </c>
       <c r="E12" t="n">
-        <v>51.84</v>
+        <v>41.07</v>
       </c>
       <c r="F12" t="n">
-        <v>51.84</v>
+        <v>41.07</v>
       </c>
       <c r="G12" t="n">
-        <v>76.78</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>3087931</v>
+        <v>5319436</v>
       </c>
       <c r="E13" t="n">
-        <v>23.22</v>
+        <v>40.01</v>
       </c>
       <c r="F13" t="n">
-        <v>23.22</v>
+        <v>40.01</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>81.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>2515542</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+        <v>18.92</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>5461080</v>
+        <v>1735968</v>
       </c>
       <c r="E15" t="n">
-        <v>41.07</v>
+        <v>13.06</v>
       </c>
       <c r="F15" t="n">
-        <v>41.07</v>
+        <v>13.06</v>
       </c>
       <c r="G15" t="n">
-        <v>41.07</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>5319436</v>
+        <v>4120618</v>
       </c>
       <c r="E16" t="n">
-        <v>40.01</v>
+        <v>30.99</v>
       </c>
       <c r="F16" t="n">
-        <v>40.01</v>
+        <v>30.99</v>
       </c>
       <c r="G16" t="n">
-        <v>81.08</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>2515542</v>
+        <v>859443</v>
       </c>
       <c r="E17" t="n">
-        <v>18.92</v>
+        <v>6.46</v>
       </c>
       <c r="F17" t="n">
-        <v>18.92</v>
+        <v>6.46</v>
       </c>
       <c r="G17" t="n">
-        <v>100</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>6580029</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+        <v>49.49</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>1735968</v>
+        <v>9747402</v>
       </c>
       <c r="E19" t="n">
-        <v>13.06</v>
+        <v>73.31</v>
       </c>
       <c r="F19" t="n">
-        <v>13.06</v>
+        <v>73.31</v>
       </c>
       <c r="G19" t="n">
-        <v>13.06</v>
+        <v>73.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>4120618</v>
+        <v>3548656</v>
       </c>
       <c r="E20" t="n">
-        <v>30.99</v>
+        <v>26.69</v>
       </c>
       <c r="F20" t="n">
-        <v>30.99</v>
+        <v>26.69</v>
       </c>
       <c r="G20" t="n">
-        <v>44.05</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" t="n">
-        <v>859443</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="G21" t="n">
-        <v>50.51</v>
+      <c r="A21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>6580029</v>
+        <v>12599850</v>
       </c>
       <c r="E22" t="n">
-        <v>49.49</v>
+        <v>94.76</v>
       </c>
       <c r="F22" t="n">
-        <v>49.49</v>
+        <v>94.76</v>
       </c>
       <c r="G22" t="n">
+        <v>94.76</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="n">
+        <v>696208</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="G23" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2" t="n">
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" t="n">
+      <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9747402</v>
-      </c>
-      <c r="E24" t="n">
-        <v>73.31</v>
-      </c>
-      <c r="F24" t="n">
-        <v>73.31</v>
-      </c>
-      <c r="G24" t="n">
-        <v>73.31</v>
+      <c r="G24" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D25" t="n">
-        <v>3548656</v>
+        <v>3345381</v>
       </c>
       <c r="E25" t="n">
-        <v>26.69</v>
+        <v>25.16</v>
       </c>
       <c r="F25" t="n">
-        <v>26.69</v>
+        <v>25.16</v>
       </c>
       <c r="G25" t="n">
-        <v>100</v>
+        <v>25.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B26" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>4368708</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>32.86</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>32.86</v>
       </c>
       <c r="G26" t="n">
-        <v>100</v>
+        <v>58.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>5581969</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+        <v>41.98</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D28" t="n">
-        <v>12599850</v>
+        <v>3293698</v>
       </c>
       <c r="E28" t="n">
-        <v>94.76</v>
+        <v>24.77</v>
       </c>
       <c r="F28" t="n">
-        <v>94.76</v>
+        <v>24.77</v>
       </c>
       <c r="G28" t="n">
-        <v>94.76</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D29" t="n">
-        <v>696208</v>
+        <v>4517171</v>
       </c>
       <c r="E29" t="n">
-        <v>5.24</v>
+        <v>33.97</v>
       </c>
       <c r="F29" t="n">
-        <v>5.24</v>
+        <v>33.97</v>
       </c>
       <c r="G29" t="n">
+        <v>58.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>5485189</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" t="n">
-        <v>96</v>
-      </c>
-      <c r="C30" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" t="n">
+    <row r="31">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10230366</v>
+      </c>
+      <c r="E31" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="F31" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="G31" t="n">
+        <v>76.94</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D32" t="n">
-        <v>3345381</v>
+        <v>3050525</v>
       </c>
       <c r="E32" t="n">
-        <v>25.16</v>
+        <v>22.94</v>
       </c>
       <c r="F32" t="n">
-        <v>25.16</v>
+        <v>22.94</v>
       </c>
       <c r="G32" t="n">
-        <v>25.16</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D33" t="n">
-        <v>4368708</v>
+        <v>13789</v>
       </c>
       <c r="E33" t="n">
-        <v>32.86</v>
+        <v>0.1</v>
       </c>
       <c r="F33" t="n">
-        <v>32.86</v>
+        <v>0.1</v>
       </c>
       <c r="G33" t="n">
-        <v>58.02</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" t="n">
-        <v>5581969</v>
-      </c>
-      <c r="E34" t="n">
-        <v>41.98</v>
-      </c>
-      <c r="F34" t="n">
-        <v>41.98</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="A34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1378</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2" t="n">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
+      <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5636625</v>
+      </c>
+      <c r="E35" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="F35" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="G35" t="n">
+        <v>42.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D36" t="n">
-        <v>3293698</v>
+        <v>7644266</v>
       </c>
       <c r="E36" t="n">
-        <v>24.77</v>
+        <v>57.49</v>
       </c>
       <c r="F36" t="n">
-        <v>24.77</v>
+        <v>57.49</v>
       </c>
       <c r="G36" t="n">
-        <v>24.77</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D37" t="n">
-        <v>4517171</v>
+        <v>13789</v>
       </c>
       <c r="E37" t="n">
-        <v>33.97</v>
+        <v>0.1</v>
       </c>
       <c r="F37" t="n">
-        <v>33.97</v>
+        <v>0.1</v>
       </c>
       <c r="G37" t="n">
-        <v>58.75</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>5485189</v>
-      </c>
-      <c r="E38" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="F38" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="A38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1378</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G38" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2" t="n">
+      <c r="A39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
+      <c r="C39" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5649284</v>
+      </c>
+      <c r="E39" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="F39" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="G39" t="n">
+        <v>42.49</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D40" t="n">
-        <v>10230366</v>
+        <v>7631608</v>
       </c>
       <c r="E40" t="n">
-        <v>76.94</v>
+        <v>57.4</v>
       </c>
       <c r="F40" t="n">
-        <v>76.94</v>
+        <v>57.4</v>
       </c>
       <c r="G40" t="n">
-        <v>76.94</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D41" t="n">
-        <v>3050525</v>
+        <v>13789</v>
       </c>
       <c r="E41" t="n">
-        <v>22.94</v>
+        <v>0.1</v>
       </c>
       <c r="F41" t="n">
-        <v>22.94</v>
+        <v>0.1</v>
       </c>
       <c r="G41" t="n">
-        <v>99.89</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" t="n">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" t="n">
-        <v>13789</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>99.99</v>
+      <c r="A42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1378</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B43" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D43" t="n">
-        <v>1378</v>
+        <v>5167184</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01</v>
+        <v>38.86</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01</v>
+        <v>38.86</v>
       </c>
       <c r="G43" t="n">
-        <v>100</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
+      <c r="A44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8113707</v>
+      </c>
+      <c r="E44" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="F44" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="G44" t="n">
+        <v>99.89</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D45" t="n">
-        <v>5636625</v>
+        <v>13789</v>
       </c>
       <c r="E45" t="n">
-        <v>42.39</v>
+        <v>0.1</v>
       </c>
       <c r="F45" t="n">
-        <v>42.39</v>
+        <v>0.1</v>
       </c>
       <c r="G45" t="n">
-        <v>42.39</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" t="n">
-        <v>7644266</v>
-      </c>
-      <c r="E46" t="n">
-        <v>57.49</v>
-      </c>
-      <c r="F46" t="n">
-        <v>57.49</v>
-      </c>
-      <c r="G46" t="n">
-        <v>99.89</v>
+      <c r="A46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>1378</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B47" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D47" t="n">
-        <v>13789</v>
+        <v>6704142</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1</v>
+        <v>50.42</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1</v>
+        <v>50.42</v>
       </c>
       <c r="G47" t="n">
-        <v>99.99</v>
+        <v>50.42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B48" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D48" t="n">
-        <v>1378</v>
+        <v>6576750</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>49.46</v>
       </c>
       <c r="F48" t="n">
-        <v>0.01</v>
+        <v>49.46</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
+      <c r="A49" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" t="n">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" t="n">
+        <v>13789</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>99.99</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D50" t="n">
-        <v>5649284</v>
+        <v>1378</v>
       </c>
       <c r="E50" t="n">
-        <v>42.49</v>
+        <v>0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>42.49</v>
+        <v>0.01</v>
       </c>
       <c r="G50" t="n">
-        <v>42.49</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" t="n">
-        <v>7631608</v>
-      </c>
-      <c r="E51" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="F51" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="G51" t="n">
-        <v>99.89</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" t="n">
-        <v>88</v>
-      </c>
-      <c r="C52" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" t="n">
-        <v>13789</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G52" t="n">
-        <v>99.99</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53" t="n">
-        <v>99</v>
-      </c>
-      <c r="C53" t="s">
-        <v>49</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1378</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G53" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" t="s">
-        <v>57</v>
-      </c>
-      <c r="D55" t="n">
-        <v>5167184</v>
-      </c>
-      <c r="E55" t="n">
-        <v>38.86</v>
-      </c>
-      <c r="F55" t="n">
-        <v>38.86</v>
-      </c>
-      <c r="G55" t="n">
-        <v>38.86</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>58</v>
-      </c>
-      <c r="D56" t="n">
-        <v>8113707</v>
-      </c>
-      <c r="E56" t="n">
-        <v>61.02</v>
-      </c>
-      <c r="F56" t="n">
-        <v>61.02</v>
-      </c>
-      <c r="G56" t="n">
-        <v>99.89</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" t="n">
-        <v>88</v>
-      </c>
-      <c r="C57" t="s">
-        <v>48</v>
-      </c>
-      <c r="D57" t="n">
-        <v>13789</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>99.99</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>56</v>
-      </c>
-      <c r="B58" t="n">
-        <v>99</v>
-      </c>
-      <c r="C58" t="s">
-        <v>49</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1378</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G58" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" t="s">
-        <v>60</v>
-      </c>
-      <c r="D60" t="n">
-        <v>6704142</v>
-      </c>
-      <c r="E60" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="F60" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="G60" t="n">
-        <v>50.42</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="s">
-        <v>61</v>
-      </c>
-      <c r="D61" t="n">
-        <v>6576750</v>
-      </c>
-      <c r="E61" t="n">
-        <v>49.46</v>
-      </c>
-      <c r="F61" t="n">
-        <v>49.46</v>
-      </c>
-      <c r="G61" t="n">
-        <v>99.89</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>59</v>
-      </c>
-      <c r="B62" t="n">
-        <v>88</v>
-      </c>
-      <c r="C62" t="s">
-        <v>48</v>
-      </c>
-      <c r="D62" t="n">
-        <v>13789</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>99.99</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" t="n">
-        <v>99</v>
-      </c>
-      <c r="C63" t="s">
-        <v>49</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1378</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G63" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64"/>
-      <c r="C64"/>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64"/>
-      <c r="G64"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>

--- a/output/tables/2025/tabla3_variables_secundarias.xlsx
+++ b/output/tables/2025/tabla3_variables_secundarias.xlsx
@@ -1151,16 +1151,16 @@
         <v>38</v>
       </c>
       <c r="D25" t="n">
-        <v>3345381</v>
+        <v>3828471</v>
       </c>
       <c r="E25" t="n">
-        <v>25.16</v>
+        <v>28.84</v>
       </c>
       <c r="F25" t="n">
-        <v>25.16</v>
+        <v>28.84</v>
       </c>
       <c r="G25" t="n">
-        <v>25.16</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="26">
@@ -1174,16 +1174,16 @@
         <v>39</v>
       </c>
       <c r="D26" t="n">
-        <v>4368708</v>
+        <v>3999377</v>
       </c>
       <c r="E26" t="n">
-        <v>32.86</v>
+        <v>30.12</v>
       </c>
       <c r="F26" t="n">
-        <v>32.86</v>
+        <v>30.12</v>
       </c>
       <c r="G26" t="n">
-        <v>58.02</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="27">
@@ -1197,13 +1197,13 @@
         <v>40</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>5581969</v>
+        <v>5449296</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>41.98</v>
+        <v>41.04</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>41.98</v>
+        <v>41.04</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>100</v>
@@ -1220,16 +1220,16 @@
         <v>42</v>
       </c>
       <c r="D28" t="n">
-        <v>3293698</v>
+        <v>3291585</v>
       </c>
       <c r="E28" t="n">
-        <v>24.77</v>
+        <v>24.81</v>
       </c>
       <c r="F28" t="n">
-        <v>24.77</v>
+        <v>24.81</v>
       </c>
       <c r="G28" t="n">
-        <v>24.77</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="29">
@@ -1243,16 +1243,16 @@
         <v>43</v>
       </c>
       <c r="D29" t="n">
-        <v>4517171</v>
+        <v>4788733</v>
       </c>
       <c r="E29" t="n">
-        <v>33.97</v>
+        <v>36.1</v>
       </c>
       <c r="F29" t="n">
-        <v>33.97</v>
+        <v>36.1</v>
       </c>
       <c r="G29" t="n">
-        <v>58.75</v>
+        <v>60.91</v>
       </c>
     </row>
     <row r="30">
@@ -1266,13 +1266,13 @@
         <v>44</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>5485189</v>
+        <v>5184718</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>41.25</v>
+        <v>39.09</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>41.25</v>
+        <v>39.09</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>100</v>

--- a/output/tables/2025/tabla3_variables_secundarias.xlsx
+++ b/output/tables/2025/tabla3_variables_secundarias.xlsx
@@ -6,26 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="AVISO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variables_secundarias" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="variables_secundarias" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t xml:space="preserve">aviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROVISIONAL - no citar como número final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D5 abierta (PLAN.md): desordenes_ind_rec e incivilidades_ind_rec pueden cambiar de mecanismo/escala. El resto de VARS_SEC no depende de D5.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -551,33 +538,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="3.71" hidden="0" customWidth="1"/>
@@ -590,36 +550,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>6455760</v>
@@ -636,13 +596,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>6840298</v>
@@ -659,13 +619,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>1603714</v>
@@ -682,13 +642,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>5579658</v>
@@ -705,13 +665,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>6059687</v>
@@ -728,13 +688,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>32299</v>
@@ -751,13 +711,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>20699</v>
@@ -774,13 +734,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
         <v>3315823</v>
@@ -797,13 +757,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B10" t="n">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
         <v>6892304</v>
@@ -820,13 +780,13 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>3087931</v>
@@ -843,13 +803,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>5461080</v>
@@ -866,13 +826,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
         <v>5319436</v>
@@ -889,13 +849,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2515542</v>
@@ -912,13 +872,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
         <v>1735968</v>
@@ -935,13 +895,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
         <v>4120618</v>
@@ -958,13 +918,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
         <v>859443</v>
@@ -981,13 +941,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>6580029</v>
@@ -1004,13 +964,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>9747402</v>
@@ -1027,13 +987,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D20" t="n">
         <v>3548656</v>
@@ -1050,13 +1010,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>96</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
@@ -1073,13 +1033,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
         <v>12599850</v>
@@ -1096,13 +1056,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D23" t="n">
         <v>696208</v>
@@ -1119,13 +1079,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>96</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
@@ -1142,13 +1102,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D25" t="n">
         <v>3828471</v>
@@ -1165,13 +1125,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B26" t="n">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D26" t="n">
         <v>3999377</v>
@@ -1188,13 +1148,13 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>5449296</v>
@@ -1211,13 +1171,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D28" t="n">
         <v>3291585</v>
@@ -1234,13 +1194,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D29" t="n">
         <v>4788733</v>
@@ -1257,13 +1217,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>5184718</v>
@@ -1280,13 +1240,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D31" t="n">
         <v>10230366</v>
@@ -1303,13 +1263,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D32" t="n">
         <v>3050525</v>
@@ -1326,13 +1286,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B33" t="n">
         <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D33" t="n">
         <v>13789</v>
@@ -1349,13 +1309,13 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>1378</v>
@@ -1372,13 +1332,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D35" t="n">
         <v>5636625</v>
@@ -1395,13 +1355,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>7644266</v>
@@ -1418,13 +1378,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B37" t="n">
         <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D37" t="n">
         <v>13789</v>
@@ -1441,13 +1401,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>1378</v>
@@ -1464,13 +1424,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D39" t="n">
         <v>5649284</v>
@@ -1487,13 +1447,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D40" t="n">
         <v>7631608</v>
@@ -1510,13 +1470,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B41" t="n">
         <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D41" t="n">
         <v>13789</v>
@@ -1533,13 +1493,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>1378</v>
@@ -1556,13 +1516,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D43" t="n">
         <v>5167184</v>
@@ -1579,13 +1539,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D44" t="n">
         <v>8113707</v>
@@ -1602,13 +1562,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B45" t="n">
         <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D45" t="n">
         <v>13789</v>
@@ -1625,13 +1585,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>1378</v>
@@ -1648,13 +1608,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D47" t="n">
         <v>6704142</v>
@@ -1671,13 +1631,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D48" t="n">
         <v>6576750</v>
@@ -1694,13 +1654,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B49" t="n">
         <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D49" t="n">
         <v>13789</v>
@@ -1717,13 +1677,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B50" t="n">
         <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D50" t="n">
         <v>1378</v>

--- a/output/tables/2025/tabla3_variables_secundarias.xlsx
+++ b/output/tables/2025/tabla3_variables_secundarias.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -137,6 +137,30 @@
     <t xml:space="preserve">Alta percepción de incivilidades</t>
   </si>
   <si>
+    <t xml:space="preserve">p_aumento_pais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aumentó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se mantuvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disminuyó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No sabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No responde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_barrio</t>
+  </si>
+  <si>
     <t xml:space="preserve">info_exp_personal</t>
   </si>
   <si>
@@ -144,12 +168,6 @@
   </si>
   <si>
     <t xml:space="preserve">Se informa por experiencia personal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No sabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No responde</t>
   </si>
   <si>
     <t xml:space="preserve">info_otras_personas</t>
@@ -1243,22 +1261,22 @@
         <v>41</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
         <v>42</v>
       </c>
       <c r="D31" t="n">
-        <v>10230366</v>
+        <v>11017721</v>
       </c>
       <c r="E31" t="n">
-        <v>76.94</v>
+        <v>82.86</v>
       </c>
       <c r="F31" t="n">
-        <v>76.94</v>
+        <v>82.86</v>
       </c>
       <c r="G31" t="n">
-        <v>76.94</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="32">
@@ -1266,22 +1284,22 @@
         <v>41</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="s">
         <v>43</v>
       </c>
       <c r="D32" t="n">
-        <v>3050525</v>
+        <v>1910607</v>
       </c>
       <c r="E32" t="n">
-        <v>22.94</v>
+        <v>14.37</v>
       </c>
       <c r="F32" t="n">
-        <v>22.94</v>
+        <v>14.37</v>
       </c>
       <c r="G32" t="n">
-        <v>99.89</v>
+        <v>97.23</v>
       </c>
     </row>
     <row r="33">
@@ -1289,226 +1307,226 @@
         <v>41</v>
       </c>
       <c r="B33" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="C33" t="s">
         <v>44</v>
       </c>
       <c r="D33" t="n">
-        <v>13789</v>
+        <v>285860</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1</v>
+        <v>2.15</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1</v>
+        <v>2.15</v>
       </c>
       <c r="G33" t="n">
-        <v>99.99</v>
+        <v>99.38</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="s">
+      <c r="A34" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="B34" t="n">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="2" t="n">
-        <v>1378</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>100</v>
+      <c r="D34" t="n">
+        <v>77880</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G34" t="n">
+        <v>99.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>99.97</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" t="n">
-        <v>5636625</v>
-      </c>
-      <c r="E35" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="F35" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="G35" t="n">
-        <v>42.39</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" t="n">
-        <v>7644266</v>
-      </c>
-      <c r="E36" t="n">
-        <v>57.49</v>
-      </c>
-      <c r="F36" t="n">
-        <v>57.49</v>
-      </c>
-      <c r="G36" t="n">
-        <v>99.89</v>
+      <c r="D36" s="2" t="n">
+        <v>3990</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D37" t="n">
-        <v>13789</v>
+        <v>9375075</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1</v>
+        <v>70.51</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1</v>
+        <v>70.51</v>
       </c>
       <c r="G37" t="n">
-        <v>99.99</v>
+        <v>70.51</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>1378</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>100</v>
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3226996</v>
+      </c>
+      <c r="E38" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="F38" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="G38" t="n">
+        <v>94.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D39" t="n">
-        <v>5649284</v>
+        <v>473732</v>
       </c>
       <c r="E39" t="n">
-        <v>42.49</v>
+        <v>3.56</v>
       </c>
       <c r="F39" t="n">
-        <v>42.49</v>
+        <v>3.56</v>
       </c>
       <c r="G39" t="n">
-        <v>42.49</v>
+        <v>98.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>7631608</v>
+        <v>214812</v>
       </c>
       <c r="E40" t="n">
-        <v>57.4</v>
+        <v>1.62</v>
       </c>
       <c r="F40" t="n">
-        <v>57.4</v>
+        <v>1.62</v>
       </c>
       <c r="G40" t="n">
-        <v>99.89</v>
+        <v>99.96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B41" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D41" t="n">
-        <v>13789</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>99.99</v>
+        <v>99.96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1378</v>
+        <v>5444</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>100</v>
@@ -1516,185 +1534,599 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D43" t="n">
-        <v>5167184</v>
+        <v>6272481</v>
       </c>
       <c r="E43" t="n">
-        <v>38.86</v>
+        <v>47.18</v>
       </c>
       <c r="F43" t="n">
-        <v>38.86</v>
+        <v>47.18</v>
       </c>
       <c r="G43" t="n">
-        <v>38.86</v>
+        <v>47.18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D44" t="n">
-        <v>8113707</v>
+        <v>5827715</v>
       </c>
       <c r="E44" t="n">
-        <v>61.02</v>
+        <v>43.83</v>
       </c>
       <c r="F44" t="n">
-        <v>61.02</v>
+        <v>43.83</v>
       </c>
       <c r="G44" t="n">
-        <v>99.89</v>
+        <v>91.01</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
         <v>44</v>
       </c>
       <c r="D45" t="n">
-        <v>13789</v>
+        <v>968916</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1</v>
+        <v>7.29</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1</v>
+        <v>7.29</v>
       </c>
       <c r="G45" t="n">
-        <v>99.99</v>
+        <v>98.29</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" t="n">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="2" t="n">
-        <v>1378</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>100</v>
+      <c r="D46" t="n">
+        <v>218625</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G46" t="n">
+        <v>99.94</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>6704142</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>50.42</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>50.42</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>50.42</v>
+        <v>99.94</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" t="n">
-        <v>6576750</v>
-      </c>
-      <c r="E48" t="n">
-        <v>49.46</v>
-      </c>
-      <c r="F48" t="n">
-        <v>49.46</v>
-      </c>
-      <c r="G48" t="n">
-        <v>99.89</v>
+      <c r="A48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>8321</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B49" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>13789</v>
+        <v>10230366</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1</v>
+        <v>76.94</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1</v>
+        <v>76.94</v>
       </c>
       <c r="G49" t="n">
-        <v>99.99</v>
+        <v>76.94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3050525</v>
+      </c>
+      <c r="E50" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="G50" t="n">
+        <v>99.89</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>88</v>
+      </c>
+      <c r="C51" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" t="n">
+        <v>13789</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>99.99</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1378</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5636625</v>
+      </c>
+      <c r="E53" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="F53" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="G53" t="n">
+        <v>42.39</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" t="n">
+        <v>7644266</v>
+      </c>
+      <c r="E54" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="F54" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="G54" t="n">
+        <v>99.89</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" t="n">
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" t="n">
+        <v>13789</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>99.99</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>1378</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
         <v>55</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5649284</v>
+      </c>
+      <c r="E57" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="F57" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="G57" t="n">
+        <v>42.49</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7631608</v>
+      </c>
+      <c r="E58" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="G58" t="n">
+        <v>99.89</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>55</v>
+      </c>
+      <c r="B59" t="n">
+        <v>88</v>
+      </c>
+      <c r="C59" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" t="n">
+        <v>13789</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>99.99</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1378</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5167184</v>
+      </c>
+      <c r="E61" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="F61" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="G61" t="n">
+        <v>38.86</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>58</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" t="n">
+        <v>8113707</v>
+      </c>
+      <c r="E62" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="F62" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="G62" t="n">
+        <v>99.89</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>58</v>
+      </c>
+      <c r="B63" t="n">
+        <v>88</v>
+      </c>
+      <c r="C63" t="s">
         <v>45</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D63" t="n">
+        <v>13789</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>99.99</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64" s="2" t="n">
         <v>1378</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E64" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F64" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G64" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="s">
+        <v>62</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6704142</v>
+      </c>
+      <c r="E65" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="F65" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="G65" t="n">
+        <v>50.42</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" t="n">
+        <v>6576750</v>
+      </c>
+      <c r="E66" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="F66" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="G66" t="n">
+        <v>99.89</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>61</v>
+      </c>
+      <c r="B67" t="n">
+        <v>88</v>
+      </c>
+      <c r="C67" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" t="n">
+        <v>13789</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>99.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>61</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99</v>
+      </c>
+      <c r="C68" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1378</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G68" t="n">
         <v>100</v>
       </c>
     </row>
